--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486857_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486857_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3779</v>
+        <v>1.9866</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4443</v>
+        <v>3.0531</v>
       </c>
       <c r="F2" t="n">
         <v>-1.0664</v>
@@ -610,10 +610,10 @@
         <v>1.0267</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0499</v>
+        <v>0.6586</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8677</v>
+        <v>0.4765</v>
       </c>
       <c r="U2" t="n">
         <v>0.1822</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7726</v>
+        <v>0.2821</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7311</v>
+        <v>2.399</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5037</v>
+        <v>-2.1168</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0074</v>
+        <v>-1.667</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2362</v>
+        <v>0.3829</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2288</v>
+        <v>-2.0499</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0168</v>
+        <v>-1.0446</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8984</v>
+        <v>0.403</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1184</v>
+        <v>-1.4476</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0094</v>
+        <v>-0.6224</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6623</v>
+        <v>-0.0201</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3472</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2588</v>
+        <v>-1.2321</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0534</v>
+        <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6687</v>
+        <v>-0.8804</v>
       </c>
       <c r="T3" t="n">
-        <v>0.209</v>
+        <v>-0.0389</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4597</v>
+        <v>-0.8415</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6982</v>
+        <v>1.5975</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6982</v>
+        <v>4.7145</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-3.117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>A. BALADA SEGOVIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1947</v>
+        <v>0.2492</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.3681</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1947</v>
+        <v>-0.119</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1947</v>
+        <v>-0.2293</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1947</v>
+        <v>-0.0975</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0.1318</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0.0929</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.0389</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.1318</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1947</v>
+        <v>-0.1365</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1947</v>
+        <v>-0.1365</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.1375</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.461</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.5985</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BALADA SEGOVIA</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3216</v>
+        <v>0.1756</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1433</v>
+        <v>-0.9132</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1783</v>
+        <v>1.0887</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2293</v>
+        <v>1.0074</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0975</v>
+        <v>1.2362</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1318</v>
+        <v>-0.2288</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0929</v>
+        <v>2.0168</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0389</v>
+        <v>1.8984</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1318</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1365</v>
+        <v>-1.0094</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1365</v>
+        <v>-0.6623</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.3472</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R5" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7082000000000001</v>
+        <v>0.0717</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0504</v>
+        <v>0.0269</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6578000000000001</v>
+        <v>0.0447</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8476</v>
+        <v>-0.1947</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1722</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0198</v>
+        <v>-0.1947</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.28</v>
+        <v>-0.1947</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2065</v>
+        <v>-0.1947</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0736</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5258</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6837</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1579</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7542</v>
+        <v>-0.1947</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5228</v>
+        <v>-0.1947</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2314</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0267</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2537</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9568</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.703</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1787</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>A. ROIG BARBERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.6523</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1282</v>
+        <v>-0.6112</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0279</v>
+        <v>-0.0411</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.667</v>
+        <v>-0.073</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3829</v>
+        <v>0.1427</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0499</v>
+        <v>-0.2157</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0446</v>
+        <v>0.0979</v>
       </c>
       <c r="K7" t="n">
-        <v>0.403</v>
+        <v>0.0584</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4476</v>
+        <v>0.0395</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6224</v>
+        <v>-0.1709</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0201</v>
+        <v>0.0843</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.2552</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2321</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4641</v>
+        <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0623</v>
+        <v>0.2421</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3097</v>
+        <v>0.0775</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7526</v>
+        <v>0.1647</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5975</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>4.7145</v>
+        <v>0.2402</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.117</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ROIG BARBERA</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9208</v>
+        <v>-1.2166</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8204</v>
+        <v>0.9514</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1004</v>
+        <v>-2.168</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.073</v>
+        <v>-1.28</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1427</v>
+        <v>-1.2065</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2157</v>
+        <v>-0.0736</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0979</v>
+        <v>-0.5258</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0584</v>
+        <v>-0.6837</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0395</v>
+        <v>0.1579</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1709</v>
+        <v>-0.7542</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0843</v>
+        <v>-0.5228</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2552</v>
+        <v>-0.2314</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0263</v>
+        <v>-0.1153</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1317</v>
+        <v>0.736</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1054</v>
+        <v>-0.8512999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1787</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2402</v>
+        <v>1.7679</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2402</v>
+        <v>-1.5893</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6594</v>
+        <v>-2.664</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8576</v>
+        <v>0.4465</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.517</v>
+        <v>-3.1105</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5574</v>
+        <v>0.1646</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7868</v>
+        <v>-0.9508</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3442</v>
+        <v>1.1154</v>
       </c>
       <c r="J9" t="n">
-        <v>0.835</v>
+        <v>1.5004</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3222</v>
+        <v>0.4088</v>
       </c>
       <c r="L9" t="n">
-        <v>3.1573</v>
+        <v>1.0916</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2776</v>
+        <v>-1.3358</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4646</v>
+        <v>-1.3596</v>
       </c>
       <c r="O9" t="n">
-        <v>0.187</v>
+        <v>0.0238</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8481</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0534</v>
+        <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5906</v>
+        <v>-0.2393</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9877</v>
+        <v>-0.0272</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5783</v>
+        <v>-0.2121</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.4743</v>
+        <v>-2.1786</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.7145</v>
+        <v>-2.1786</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0528</v>
+        <v>-3.0161</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0281</v>
+        <v>1.323</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0808</v>
+        <v>-4.3391</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1646</v>
+        <v>0.5574</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9508</v>
+        <v>-2.7868</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1154</v>
+        <v>3.3442</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5004</v>
+        <v>0.835</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4088</v>
+        <v>-2.3222</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0916</v>
+        <v>3.1573</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3358</v>
+        <v>-0.2776</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3596</v>
+        <v>-0.4646</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0238</v>
+        <v>0.187</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4107</v>
+        <v>1.8481</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R10" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6281</v>
+        <v>-0.9473</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4457</v>
+        <v>0.4531</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1824</v>
+        <v>-1.4004</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1786</v>
+        <v>-4.4743</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1786</v>
+        <v>-4.7145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9282</v>
+        <v>-3.3484</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5762</v>
+        <v>0.5044</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.352</v>
+        <v>-3.8528</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4366</v>
+        <v>-0.5874</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2974</v>
+        <v>-0.2111</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.7339</v>
+        <v>-0.3763</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6171</v>
+        <v>0.8689</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5145</v>
+        <v>0.9217</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.1316</v>
+        <v>-0.0529</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8195</v>
+        <v>-1.4562</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2171</v>
+        <v>-1.1328</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.3234</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.2855</v>
+        <v>2.0534</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.3389</v>
+        <v>-0.2053</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0534</v>
+        <v>2.2588</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1265</v>
+        <v>-1.1081</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7823</v>
+        <v>-0.1591</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6558</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>2.6673</v>
+        <v>-3.7063</v>
       </c>
       <c r="W11" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0698</v>
+        <v>-3.7063</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1497</v>
+        <v>-4.2166</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0589</v>
+        <v>-4.072</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2086</v>
+        <v>-0.1445</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5874</v>
+        <v>-3.4366</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2111</v>
+        <v>1.2974</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3763</v>
+        <v>-4.7339</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8689</v>
+        <v>-1.6171</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9217</v>
+        <v>2.5145</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0529</v>
+        <v>-4.1316</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4562</v>
+        <v>-1.8195</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1328</v>
+        <v>-1.2171</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3234</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P12" t="n">
+        <v>-3.2855</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-5.3389</v>
+      </c>
+      <c r="R12" t="n">
         <v>2.0534</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-0.2053</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.2588</v>
-      </c>
       <c r="S12" t="n">
-        <v>-1.9094</v>
+        <v>-0.1618</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6046</v>
+        <v>0.2865</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3048</v>
+        <v>-0.4483</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.7063</v>
+        <v>2.6673</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.5975</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.7063</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4234</v>
+        <v>-5.9853</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.639</v>
+        <v>-4.023</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7844</v>
+        <v>-1.9623</v>
       </c>
       <c r="G13" t="n">
         <v>-2.456</v>
@@ -1468,13 +1468,13 @@
         <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8236</v>
+        <v>-0.3855</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3139</v>
+        <v>0.3021</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5097</v>
+        <v>-0.6876</v>
       </c>
       <c r="V13" t="n">
         <v>-2.117</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-20.2474</v>
+        <v>-18.6005</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.2207</v>
+        <v>-0.5738999999999992</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.0266</v>
+        <v>-18.0265</v>
       </c>
       <c r="G14" t="n">
         <v>-7.8933</v>
@@ -1516,19 +1516,19 @@
         <v>-4.169</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.7243</v>
+        <v>-3.724300000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9246999999999996</v>
+        <v>0.9247000000000005</v>
       </c>
       <c r="K14" t="n">
         <v>1.756</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8313999999999995</v>
+        <v>-0.8313999999999996</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.818</v>
+        <v>-8.818000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-5.9252</v>
@@ -1546,16 +1546,16 @@
         <v>15.4005</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.6497</v>
+        <v>-3.0028</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9474999999999998</v>
+        <v>2.5944</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.597099999999999</v>
+        <v>-5.597199999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-8.730899999999998</v>
+        <v>-8.7309</v>
       </c>
       <c r="W14" t="n">
         <v>10.2809</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9292</v>
+        <v>6.4584</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3657</v>
+        <v>5.0519</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5635</v>
+        <v>1.4065</v>
       </c>
       <c r="G15" t="n">
         <v>3.0566</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8172</v>
+        <v>1.3464</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2357</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5815</v>
+        <v>0.4245</v>
       </c>
       <c r="V15" t="n">
         <v>2.4661</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5103</v>
+        <v>4.9078</v>
       </c>
       <c r="E16" t="n">
         <v>3.0068</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5035</v>
+        <v>1.901</v>
       </c>
       <c r="G16" t="n">
         <v>4.5807</v>
@@ -1702,13 +1702,13 @@
         <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3394</v>
+        <v>0.0581</v>
       </c>
       <c r="T16" t="n">
         <v>0.2362</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5756</v>
+        <v>-0.1781</v>
       </c>
       <c r="V16" t="n">
         <v>2.117</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.9781</v>
+        <v>4.204</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6348</v>
+        <v>4.7739</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3433</v>
+        <v>-0.5699</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9371</v>
+        <v>-0.2172</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9106</v>
+        <v>-0.341</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0264</v>
+        <v>0.1238</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2207</v>
+        <v>1.6681</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1023</v>
+        <v>0.4317</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1184</v>
+        <v>1.2365</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2836</v>
+        <v>-1.8853</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1917</v>
+        <v>-0.7726</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.092</v>
+        <v>-1.1127</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.2344</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9336</v>
+        <v>0.1161</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3998</v>
+        <v>0.1183</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4805</v>
+        <v>3.7761</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4805</v>
+        <v>4.0164</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.5589</v>
+        <v>3.5876</v>
       </c>
       <c r="E18" t="n">
-        <v>4.5647</v>
+        <v>3.0072</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0058</v>
+        <v>0.5804</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2172</v>
+        <v>1.9371</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.341</v>
+        <v>1.9106</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1238</v>
+        <v>0.0264</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6681</v>
+        <v>2.2207</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4317</v>
+        <v>2.1023</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2365</v>
+        <v>0.1184</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8853</v>
+        <v>-0.2836</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7726</v>
+        <v>-0.1917</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1127</v>
+        <v>-0.092</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4107</v>
+        <v>0.1433</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0931</v>
+        <v>0.306</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3176</v>
+        <v>-0.1626</v>
       </c>
       <c r="V18" t="n">
-        <v>3.7761</v>
+        <v>0.4805</v>
       </c>
       <c r="W18" t="n">
-        <v>4.0164</v>
+        <v>0.4805</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3853</v>
+        <v>2.4097</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1102</v>
+        <v>1.7964</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2752</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>1.1435</v>
@@ -1936,13 +1936,13 @@
         <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1144</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4997</v>
+        <v>0.1859</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4098</v>
+        <v>-0.0716</v>
       </c>
       <c r="V19" t="n">
         <v>1.7679</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SANTANA LUCHORO</t>
+          <t>K. GREELEY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5572</v>
+        <v>2.1452</v>
       </c>
       <c r="E20" t="n">
-        <v>2.812</v>
+        <v>1.746</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2549</v>
+        <v>0.3992</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4453</v>
+        <v>-2.1977</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1453</v>
+        <v>-0.7164</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3</v>
+        <v>-1.4813</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4209</v>
+        <v>-1.7355</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4473</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0264</v>
+        <v>-0.7633</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0244</v>
+        <v>-0.4622</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.302</v>
+        <v>0.2559</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3264</v>
+        <v>-0.7181</v>
       </c>
       <c r="P20" t="n">
         <v>0.616</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9147</v>
+        <v>1.1294</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.7321</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1129</v>
+        <v>0.3973</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4189</v>
+        <v>2.5975</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5893</v>
+        <v>3.7761</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0082</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. GREELEY</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9422</v>
+        <v>1.0559</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1184</v>
+        <v>-0.2064</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1762</v>
+        <v>1.2623</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1977</v>
+        <v>-0.9054</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7164</v>
+        <v>-0.7134</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4813</v>
+        <v>-0.192</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7355</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.2428</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7633</v>
+        <v>-0.6579</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4622</v>
+        <v>-0.0047</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2559</v>
+        <v>-0.4706</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7181</v>
+        <v>0.4659</v>
       </c>
       <c r="P21" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0736</v>
+        <v>0.3371</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1045</v>
+        <v>0.3021</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1781</v>
+        <v>0.035</v>
       </c>
       <c r="V21" t="n">
-        <v>2.5975</v>
+        <v>1.4189</v>
       </c>
       <c r="W21" t="n">
-        <v>3.7761</v>
+        <v>1.4189</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>J. SANTANA LUCHORO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8956</v>
+        <v>0.8546</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2064</v>
+        <v>2.0798</v>
       </c>
       <c r="F22" t="n">
-        <v>1.102</v>
+        <v>-1.2252</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9054</v>
+        <v>1.4453</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7134</v>
+        <v>1.1453</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.192</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9006999999999999</v>
+        <v>1.4209</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2428</v>
+        <v>1.4473</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6579</v>
+        <v>-0.0264</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0047</v>
+        <v>0.0244</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4706</v>
+        <v>-0.302</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4659</v>
+        <v>0.3264</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1767</v>
+        <v>0.2122</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3021</v>
+        <v>0.0696</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1254</v>
+        <v>0.1425</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4189</v>
+        <v>-1.4189</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4189</v>
+        <v>0.5893</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.101</v>
+        <v>0.6817</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8115</v>
+        <v>-0.0793</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7105</v>
+        <v>0.761</v>
       </c>
       <c r="G23" t="n">
         <v>0.0197</v>
@@ -2248,13 +2248,13 @@
         <v>1.6427</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2469</v>
+        <v>1.0297</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0931</v>
+        <v>0.6391</v>
       </c>
       <c r="U23" t="n">
-        <v>0.34</v>
+        <v>0.3905</v>
       </c>
       <c r="V23" t="n">
         <v>1.0698</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0908</v>
+        <v>-0.6694</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9771</v>
+        <v>0.3827</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1136</v>
+        <v>-1.0521</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4465</v>
@@ -2326,13 +2326,13 @@
         <v>2.2588</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7161999999999999</v>
+        <v>0.7052</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5928</v>
+        <v>0.767</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1234</v>
+        <v>-0.0618</v>
       </c>
       <c r="V24" t="n">
         <v>-3.1868</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3178</v>
+        <v>-3.247</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5909</v>
+        <v>-3.5324</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2732</v>
+        <v>0.2853</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5227000000000001</v>
@@ -2404,13 +2404,13 @@
         <v>1.2321</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4103</v>
+        <v>1.481</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2624</v>
+        <v>1.321</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1478</v>
+        <v>0.16</v>
       </c>
       <c r="V25" t="n">
         <v>-2.3573</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>20.2472</v>
+        <v>22.3885</v>
       </c>
       <c r="E26" t="n">
-        <v>18.0267</v>
+        <v>18.0266</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2207</v>
+        <v>4.3619</v>
       </c>
       <c r="G26" t="n">
         <v>7.893399999999998</v>
@@ -2470,7 +2470,7 @@
         <v>-1.756</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8311999999999998</v>
+        <v>0.8311999999999999</v>
       </c>
       <c r="P26" t="n">
         <v>-1.0268</v>
@@ -2482,13 +2482,13 @@
         <v>14.374</v>
       </c>
       <c r="S26" t="n">
-        <v>4.6496</v>
+        <v>6.7912</v>
       </c>
       <c r="T26" t="n">
-        <v>5.597099999999999</v>
+        <v>5.597</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9475</v>
+        <v>1.194</v>
       </c>
       <c r="V26" t="n">
         <v>8.730800000000002</v>
